--- a/all reports/Discounts.xlsx
+++ b/all reports/Discounts.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D7C2CC0-55BC-4455-A183-A00CB64FB0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74569CC7-43EB-406C-8FB1-9384B79804F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C7BEEE38-8A0B-4642-9C60-BC2A8CB5A22E}"/>
   </bookViews>
@@ -197,19 +197,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -537,46 +531,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="6:8" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="3">
-        <v>12</v>
-      </c>
-      <c r="H2" s="3">
+      <c r="G2" s="1">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="3">
-        <v>10</v>
-      </c>
-      <c r="H3" s="3">
+      <c r="G3" s="1">
+        <v>10</v>
+      </c>
+      <c r="H3" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3">
-        <v>12</v>
-      </c>
-      <c r="H4" s="3">
+      <c r="G4" s="1">
+        <v>12</v>
+      </c>
+      <c r="H4" s="1">
         <v>5</v>
       </c>
     </row>
@@ -587,7 +581,7 @@
       <c r="G5" s="2">
         <v>12</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="1">
         <v>5</v>
       </c>
     </row>
@@ -757,145 +751,145 @@
       </c>
     </row>
     <row r="21" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="4">
-        <v>12</v>
-      </c>
-      <c r="H21" s="4">
+      <c r="G21" s="1">
+        <v>12</v>
+      </c>
+      <c r="H21" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="4">
+      <c r="G22" s="1">
         <v>15</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="4">
-        <v>12</v>
-      </c>
-      <c r="H23" s="4">
+      <c r="G23" s="1">
+        <v>12</v>
+      </c>
+      <c r="H23" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="4">
-        <v>10</v>
-      </c>
-      <c r="H24" s="4">
+      <c r="G24" s="1">
+        <v>10</v>
+      </c>
+      <c r="H24" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G25" s="4">
-        <v>12</v>
-      </c>
-      <c r="H25" s="4">
+      <c r="G25" s="1">
+        <v>12</v>
+      </c>
+      <c r="H25" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="26" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="4">
+      <c r="G26" s="1">
         <v>11</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="4">
-        <v>10</v>
-      </c>
-      <c r="H27" s="4">
+      <c r="G27" s="1">
+        <v>10</v>
+      </c>
+      <c r="H27" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="4">
-        <v>10</v>
-      </c>
-      <c r="H28" s="4">
+      <c r="G28" s="1">
+        <v>10</v>
+      </c>
+      <c r="H28" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G29" s="4">
-        <v>12</v>
-      </c>
-      <c r="H29" s="4">
+      <c r="G29" s="1">
+        <v>12</v>
+      </c>
+      <c r="H29" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G30" s="4">
-        <v>10</v>
-      </c>
-      <c r="H30" s="4">
+      <c r="G30" s="1">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G31" s="4">
-        <v>10</v>
-      </c>
-      <c r="H31" s="4">
+      <c r="G31" s="1">
+        <v>10</v>
+      </c>
+      <c r="H31" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="32" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="4">
-        <v>10</v>
-      </c>
-      <c r="H32" s="4">
+      <c r="G32" s="1">
+        <v>10</v>
+      </c>
+      <c r="H32" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="6:8" x14ac:dyDescent="0.35">
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G33" s="4">
-        <v>12</v>
-      </c>
-      <c r="H33" s="4">
+      <c r="G33" s="1">
+        <v>12</v>
+      </c>
+      <c r="H33" s="1">
         <v>5</v>
       </c>
     </row>

--- a/all reports/Discounts.xlsx
+++ b/all reports/Discounts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\all reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74569CC7-43EB-406C-8FB1-9384B79804F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E62A84E-67C8-457A-B061-628C6BC95D2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{C7BEEE38-8A0B-4642-9C60-BC2A8CB5A22E}"/>
   </bookViews>
